--- a/docs/prop-firms-bot-perso.xlsx
+++ b/docs/prop-firms-bot-perso.xlsx
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Établi le 27/09/2026. Marchés : forex / indices / matières premières en CFD, et Futures.</t>
+          <t>Établi le 28/09/2026. Marchés : forex / indices / matières premières en CFD, et Futures.</t>
         </is>
       </c>
     </row>
